--- a/outputs/Block2_National_Outcome_OOF_v12.xlsx
+++ b/outputs/Block2_National_Outcome_OOF_v12.xlsx
@@ -954,13 +954,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="E23">
-        <v>0.3420000000001255</v>
+        <v>0.3420000000001311</v>
       </c>
       <c r="F23">
-        <v>-7.657999999999876</v>
+        <v>-7.657999999999871</v>
       </c>
       <c r="G23">
-        <v>7.657999999999876</v>
+        <v>7.657999999999871</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1437,13 +1437,13 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="E44">
-        <v>-1.600400000000046</v>
+        <v>-1.600400000000041</v>
       </c>
       <c r="F44">
-        <v>5.199599999999954</v>
+        <v>5.19959999999996</v>
       </c>
       <c r="G44">
-        <v>5.199599999999954</v>
+        <v>5.19959999999996</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2886,13 +2886,13 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="E107">
-        <v>-0.4551999999999612</v>
+        <v>-0.4551999999999556</v>
       </c>
       <c r="F107">
-        <v>5.244800000000038</v>
+        <v>5.244800000000044</v>
       </c>
       <c r="G107">
-        <v>5.244800000000038</v>
+        <v>5.244800000000044</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3852,13 +3852,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E149">
-        <v>-0.5244000000000526</v>
+        <v>-0.5244000000000582</v>
       </c>
       <c r="F149">
-        <v>-9.124400000000055</v>
+        <v>-9.12440000000006</v>
       </c>
       <c r="G149">
-        <v>9.124400000000055</v>
+        <v>9.12440000000006</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4174,13 +4174,13 @@
         <v>8.600000000000001</v>
       </c>
       <c r="E163">
-        <v>-0.05467977032406202</v>
+        <v>-0.05467977032406757</v>
       </c>
       <c r="F163">
-        <v>-8.654679770324064</v>
+        <v>-8.654679770324069</v>
       </c>
       <c r="G163">
-        <v>8.654679770324064</v>
+        <v>8.654679770324069</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4335,13 +4335,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E170">
-        <v>-1.714399999999972</v>
+        <v>-1.714399999999977</v>
       </c>
       <c r="F170">
-        <v>0.9856000000000309</v>
+        <v>0.9856000000000253</v>
       </c>
       <c r="G170">
-        <v>0.9856000000000309</v>
+        <v>0.9856000000000253</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5140,13 +5140,13 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="E205">
-        <v>-1.048624949950228</v>
+        <v>-1.048624949950233</v>
       </c>
       <c r="F205">
-        <v>1.651375050049775</v>
+        <v>1.651375050049769</v>
       </c>
       <c r="G205">
-        <v>1.651375050049775</v>
+        <v>1.651375050049769</v>
       </c>
     </row>
     <row r="206" spans="1:7">
